--- a/水库项目出表/Template/图斑量算表.xlsx
+++ b/水库项目出表/Template/图斑量算表.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sunchuanhong\Local\code\水库项目出表\Template\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="360" yWindow="90" windowWidth="28035" windowHeight="12330"/>
+    <workbookView xWindow="360" yWindow="90" windowWidth="28040" windowHeight="12330"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$3:$E$1876</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$3:$G$1876</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Sheet1!$3:$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
@@ -18,15 +23,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>图斑量算表</t>
   </si>
   <si>
     <t xml:space="preserve">                </t>
-  </si>
-  <si>
-    <t>单位：公顷</t>
   </si>
   <si>
     <t>权属单位</t>
@@ -46,15 +48,27 @@
   <si>
     <t>功能分区</t>
   </si>
+  <si>
+    <t>田坎面积</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>图斑净面积</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单位：#单位#</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0000_);[Red]\(0.0000\)"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -67,11 +81,13 @@
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -79,6 +95,7 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -86,12 +103,14 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -188,11 +207,19 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -234,7 +261,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -266,9 +293,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -300,6 +328,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -475,19 +504,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F174"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H174"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.5" style="3" customWidth="1"/>
-    <col min="2" max="2" width="8.5" style="3" customWidth="1"/>
-    <col min="3" max="5" width="12.375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="11.25" style="3" customWidth="1"/>
-    <col min="7" max="7" width="9" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="22.453125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="8.453125" style="3" customWidth="1"/>
+    <col min="3" max="7" width="12.36328125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="9" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" customHeight="1">
+    <row r="1" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -496,667 +525,843 @@
       <c r="D1" s="10"/>
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
-    </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1">
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+    </row>
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="11"/>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="11"/>
+      <c r="H2" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1">
-      <c r="A3" s="4" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="G3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="H3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+    </row>
+    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="97" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="8"/>
       <c r="B97" s="8"/>
       <c r="C97" s="8"/>
       <c r="D97" s="8"/>
       <c r="E97" s="8"/>
       <c r="F97" s="8"/>
-    </row>
-    <row r="98" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G97" s="8"/>
+      <c r="H97" s="8"/>
+    </row>
+    <row r="98" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="8"/>
       <c r="B98" s="8"/>
       <c r="C98" s="8"/>
       <c r="D98" s="8"/>
       <c r="E98" s="8"/>
       <c r="F98" s="8"/>
-    </row>
-    <row r="99" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G98" s="8"/>
+      <c r="H98" s="8"/>
+    </row>
+    <row r="99" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="8"/>
       <c r="B99" s="8"/>
       <c r="C99" s="8"/>
       <c r="D99" s="8"/>
       <c r="E99" s="8"/>
       <c r="F99" s="8"/>
-    </row>
-    <row r="100" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G99" s="8"/>
+      <c r="H99" s="8"/>
+    </row>
+    <row r="100" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="8"/>
       <c r="B100" s="8"/>
       <c r="C100" s="8"/>
       <c r="D100" s="8"/>
       <c r="E100" s="8"/>
       <c r="F100" s="8"/>
-    </row>
-    <row r="101" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G100" s="8"/>
+      <c r="H100" s="8"/>
+    </row>
+    <row r="101" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="8"/>
       <c r="B101" s="8"/>
       <c r="C101" s="8"/>
       <c r="D101" s="8"/>
       <c r="E101" s="8"/>
       <c r="F101" s="8"/>
-    </row>
-    <row r="102" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G101" s="8"/>
+      <c r="H101" s="8"/>
+    </row>
+    <row r="102" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="8"/>
       <c r="B102" s="8"/>
       <c r="C102" s="8"/>
       <c r="D102" s="8"/>
       <c r="E102" s="8"/>
       <c r="F102" s="8"/>
-    </row>
-    <row r="103" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G102" s="8"/>
+      <c r="H102" s="8"/>
+    </row>
+    <row r="103" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="8"/>
       <c r="B103" s="8"/>
       <c r="C103" s="8"/>
       <c r="D103" s="8"/>
       <c r="E103" s="8"/>
       <c r="F103" s="8"/>
-    </row>
-    <row r="104" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G103" s="8"/>
+      <c r="H103" s="8"/>
+    </row>
+    <row r="104" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="8"/>
       <c r="B104" s="8"/>
       <c r="C104" s="8"/>
       <c r="D104" s="8"/>
       <c r="E104" s="8"/>
       <c r="F104" s="8"/>
-    </row>
-    <row r="105" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G104" s="8"/>
+      <c r="H104" s="8"/>
+    </row>
+    <row r="105" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="8"/>
       <c r="B105" s="8"/>
       <c r="C105" s="8"/>
       <c r="D105" s="8"/>
       <c r="E105" s="8"/>
       <c r="F105" s="8"/>
-    </row>
-    <row r="106" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G105" s="8"/>
+      <c r="H105" s="8"/>
+    </row>
+    <row r="106" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="8"/>
       <c r="B106" s="8"/>
       <c r="C106" s="8"/>
       <c r="D106" s="8"/>
       <c r="E106" s="8"/>
       <c r="F106" s="8"/>
-    </row>
-    <row r="107" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G106" s="8"/>
+      <c r="H106" s="8"/>
+    </row>
+    <row r="107" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="8"/>
       <c r="B107" s="8"/>
       <c r="C107" s="8"/>
       <c r="D107" s="8"/>
       <c r="E107" s="8"/>
       <c r="F107" s="8"/>
-    </row>
-    <row r="108" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G107" s="8"/>
+      <c r="H107" s="8"/>
+    </row>
+    <row r="108" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="8"/>
       <c r="B108" s="8"/>
       <c r="C108" s="8"/>
       <c r="D108" s="8"/>
       <c r="E108" s="8"/>
       <c r="F108" s="8"/>
-    </row>
-    <row r="109" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G108" s="8"/>
+      <c r="H108" s="8"/>
+    </row>
+    <row r="109" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="8"/>
       <c r="B109" s="8"/>
       <c r="C109" s="8"/>
       <c r="D109" s="8"/>
       <c r="E109" s="8"/>
       <c r="F109" s="8"/>
-    </row>
-    <row r="110" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G109" s="8"/>
+      <c r="H109" s="8"/>
+    </row>
+    <row r="110" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="8"/>
       <c r="B110" s="8"/>
       <c r="C110" s="8"/>
       <c r="D110" s="8"/>
       <c r="E110" s="8"/>
       <c r="F110" s="8"/>
-    </row>
-    <row r="111" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G110" s="8"/>
+      <c r="H110" s="8"/>
+    </row>
+    <row r="111" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="8"/>
       <c r="B111" s="8"/>
       <c r="C111" s="8"/>
       <c r="D111" s="8"/>
       <c r="E111" s="8"/>
       <c r="F111" s="8"/>
-    </row>
-    <row r="112" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G111" s="8"/>
+      <c r="H111" s="8"/>
+    </row>
+    <row r="112" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="8"/>
       <c r="B112" s="8"/>
       <c r="C112" s="8"/>
       <c r="D112" s="8"/>
       <c r="E112" s="8"/>
       <c r="F112" s="8"/>
-    </row>
-    <row r="113" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G112" s="8"/>
+      <c r="H112" s="8"/>
+    </row>
+    <row r="113" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="8"/>
       <c r="B113" s="8"/>
       <c r="C113" s="8"/>
       <c r="D113" s="8"/>
       <c r="E113" s="8"/>
       <c r="F113" s="8"/>
-    </row>
-    <row r="114" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G113" s="8"/>
+      <c r="H113" s="8"/>
+    </row>
+    <row r="114" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="8"/>
       <c r="B114" s="8"/>
       <c r="C114" s="8"/>
       <c r="D114" s="8"/>
       <c r="E114" s="8"/>
       <c r="F114" s="8"/>
-    </row>
-    <row r="115" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G114" s="8"/>
+      <c r="H114" s="8"/>
+    </row>
+    <row r="115" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="8"/>
       <c r="B115" s="8"/>
       <c r="C115" s="8"/>
       <c r="D115" s="8"/>
       <c r="E115" s="8"/>
       <c r="F115" s="8"/>
-    </row>
-    <row r="116" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G115" s="8"/>
+      <c r="H115" s="8"/>
+    </row>
+    <row r="116" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="8"/>
       <c r="B116" s="8"/>
       <c r="C116" s="8"/>
       <c r="D116" s="8"/>
       <c r="E116" s="8"/>
       <c r="F116" s="8"/>
-    </row>
-    <row r="117" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G116" s="8"/>
+      <c r="H116" s="8"/>
+    </row>
+    <row r="117" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="8"/>
       <c r="B117" s="8"/>
       <c r="C117" s="8"/>
       <c r="D117" s="8"/>
       <c r="E117" s="8"/>
       <c r="F117" s="8"/>
-    </row>
-    <row r="118" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G117" s="8"/>
+      <c r="H117" s="8"/>
+    </row>
+    <row r="118" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="8"/>
       <c r="B118" s="8"/>
       <c r="C118" s="8"/>
       <c r="D118" s="8"/>
       <c r="E118" s="8"/>
       <c r="F118" s="8"/>
-    </row>
-    <row r="119" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G118" s="8"/>
+      <c r="H118" s="8"/>
+    </row>
+    <row r="119" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="8"/>
       <c r="B119" s="8"/>
       <c r="C119" s="8"/>
       <c r="D119" s="8"/>
       <c r="E119" s="8"/>
       <c r="F119" s="8"/>
-    </row>
-    <row r="120" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G119" s="8"/>
+      <c r="H119" s="8"/>
+    </row>
+    <row r="120" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="8"/>
       <c r="B120" s="8"/>
       <c r="C120" s="8"/>
       <c r="D120" s="8"/>
       <c r="E120" s="8"/>
       <c r="F120" s="8"/>
-    </row>
-    <row r="121" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G120" s="8"/>
+      <c r="H120" s="8"/>
+    </row>
+    <row r="121" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="8"/>
       <c r="B121" s="8"/>
       <c r="C121" s="8"/>
       <c r="D121" s="8"/>
       <c r="E121" s="8"/>
       <c r="F121" s="8"/>
-    </row>
-    <row r="122" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G121" s="8"/>
+      <c r="H121" s="8"/>
+    </row>
+    <row r="122" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="8"/>
       <c r="B122" s="8"/>
       <c r="C122" s="8"/>
       <c r="D122" s="8"/>
       <c r="E122" s="8"/>
       <c r="F122" s="8"/>
-    </row>
-    <row r="123" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G122" s="8"/>
+      <c r="H122" s="8"/>
+    </row>
+    <row r="123" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="8"/>
       <c r="B123" s="8"/>
       <c r="C123" s="8"/>
       <c r="D123" s="8"/>
       <c r="E123" s="8"/>
       <c r="F123" s="8"/>
-    </row>
-    <row r="124" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G123" s="8"/>
+      <c r="H123" s="8"/>
+    </row>
+    <row r="124" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="8"/>
       <c r="B124" s="8"/>
       <c r="C124" s="8"/>
       <c r="D124" s="8"/>
       <c r="E124" s="8"/>
       <c r="F124" s="8"/>
-    </row>
-    <row r="125" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G124" s="8"/>
+      <c r="H124" s="8"/>
+    </row>
+    <row r="125" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="8"/>
       <c r="B125" s="8"/>
       <c r="C125" s="8"/>
       <c r="D125" s="8"/>
       <c r="E125" s="8"/>
       <c r="F125" s="8"/>
-    </row>
-    <row r="126" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G125" s="8"/>
+      <c r="H125" s="8"/>
+    </row>
+    <row r="126" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="8"/>
       <c r="B126" s="8"/>
       <c r="C126" s="8"/>
       <c r="D126" s="8"/>
       <c r="E126" s="8"/>
       <c r="F126" s="8"/>
-    </row>
-    <row r="127" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G126" s="8"/>
+      <c r="H126" s="8"/>
+    </row>
+    <row r="127" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="8"/>
       <c r="B127" s="8"/>
       <c r="C127" s="8"/>
       <c r="D127" s="8"/>
       <c r="E127" s="8"/>
       <c r="F127" s="8"/>
-    </row>
-    <row r="128" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G127" s="8"/>
+      <c r="H127" s="8"/>
+    </row>
+    <row r="128" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="8"/>
       <c r="B128" s="8"/>
       <c r="C128" s="8"/>
       <c r="D128" s="8"/>
       <c r="E128" s="8"/>
       <c r="F128" s="8"/>
-    </row>
-    <row r="129" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G128" s="8"/>
+      <c r="H128" s="8"/>
+    </row>
+    <row r="129" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="8"/>
       <c r="B129" s="8"/>
       <c r="C129" s="8"/>
       <c r="D129" s="8"/>
       <c r="E129" s="8"/>
       <c r="F129" s="8"/>
-    </row>
-    <row r="130" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G129" s="8"/>
+      <c r="H129" s="8"/>
+    </row>
+    <row r="130" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="8"/>
       <c r="B130" s="8"/>
       <c r="C130" s="8"/>
       <c r="D130" s="8"/>
       <c r="E130" s="8"/>
       <c r="F130" s="8"/>
-    </row>
-    <row r="131" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G130" s="8"/>
+      <c r="H130" s="8"/>
+    </row>
+    <row r="131" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="8"/>
       <c r="B131" s="8"/>
       <c r="C131" s="8"/>
       <c r="D131" s="8"/>
       <c r="E131" s="8"/>
       <c r="F131" s="8"/>
-    </row>
-    <row r="132" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G131" s="8"/>
+      <c r="H131" s="8"/>
+    </row>
+    <row r="132" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="8"/>
       <c r="B132" s="8"/>
       <c r="C132" s="8"/>
       <c r="D132" s="8"/>
       <c r="E132" s="8"/>
       <c r="F132" s="8"/>
-    </row>
-    <row r="133" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G132" s="8"/>
+      <c r="H132" s="8"/>
+    </row>
+    <row r="133" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="8"/>
       <c r="B133" s="8"/>
       <c r="C133" s="8"/>
       <c r="D133" s="8"/>
       <c r="E133" s="8"/>
       <c r="F133" s="8"/>
-    </row>
-    <row r="134" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G133" s="8"/>
+      <c r="H133" s="8"/>
+    </row>
+    <row r="134" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="8"/>
       <c r="B134" s="8"/>
       <c r="C134" s="8"/>
       <c r="D134" s="8"/>
       <c r="E134" s="8"/>
       <c r="F134" s="8"/>
-    </row>
-    <row r="135" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G134" s="8"/>
+      <c r="H134" s="8"/>
+    </row>
+    <row r="135" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="8"/>
       <c r="B135" s="8"/>
       <c r="C135" s="8"/>
       <c r="D135" s="8"/>
       <c r="E135" s="8"/>
       <c r="F135" s="8"/>
-    </row>
-    <row r="136" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G135" s="8"/>
+      <c r="H135" s="8"/>
+    </row>
+    <row r="136" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="8"/>
       <c r="B136" s="8"/>
       <c r="C136" s="8"/>
       <c r="D136" s="8"/>
       <c r="E136" s="8"/>
       <c r="F136" s="8"/>
-    </row>
-    <row r="137" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G136" s="8"/>
+      <c r="H136" s="8"/>
+    </row>
+    <row r="137" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="8"/>
       <c r="B137" s="8"/>
       <c r="C137" s="8"/>
       <c r="D137" s="8"/>
       <c r="E137" s="8"/>
       <c r="F137" s="8"/>
-    </row>
-    <row r="138" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G137" s="8"/>
+      <c r="H137" s="8"/>
+    </row>
+    <row r="138" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="8"/>
       <c r="B138" s="8"/>
       <c r="C138" s="8"/>
       <c r="D138" s="8"/>
       <c r="E138" s="8"/>
       <c r="F138" s="8"/>
-    </row>
-    <row r="139" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G138" s="8"/>
+      <c r="H138" s="8"/>
+    </row>
+    <row r="139" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="8"/>
       <c r="B139" s="8"/>
       <c r="C139" s="8"/>
       <c r="D139" s="8"/>
       <c r="E139" s="8"/>
       <c r="F139" s="8"/>
-    </row>
-    <row r="140" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G139" s="8"/>
+      <c r="H139" s="8"/>
+    </row>
+    <row r="140" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="8"/>
       <c r="B140" s="8"/>
       <c r="C140" s="8"/>
       <c r="D140" s="8"/>
       <c r="E140" s="8"/>
       <c r="F140" s="8"/>
-    </row>
-    <row r="141" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G140" s="8"/>
+      <c r="H140" s="8"/>
+    </row>
+    <row r="141" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="8"/>
       <c r="B141" s="8"/>
       <c r="C141" s="8"/>
       <c r="D141" s="8"/>
       <c r="E141" s="8"/>
       <c r="F141" s="8"/>
-    </row>
-    <row r="142" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G141" s="8"/>
+      <c r="H141" s="8"/>
+    </row>
+    <row r="142" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="8"/>
       <c r="B142" s="8"/>
       <c r="C142" s="8"/>
       <c r="D142" s="8"/>
       <c r="E142" s="8"/>
       <c r="F142" s="8"/>
-    </row>
-    <row r="143" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G142" s="8"/>
+      <c r="H142" s="8"/>
+    </row>
+    <row r="143" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="8"/>
       <c r="B143" s="8"/>
       <c r="C143" s="8"/>
       <c r="D143" s="8"/>
       <c r="E143" s="8"/>
       <c r="F143" s="8"/>
-    </row>
-    <row r="144" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G143" s="8"/>
+      <c r="H143" s="8"/>
+    </row>
+    <row r="144" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="8"/>
       <c r="B144" s="8"/>
       <c r="C144" s="8"/>
       <c r="D144" s="8"/>
       <c r="E144" s="8"/>
       <c r="F144" s="8"/>
-    </row>
-    <row r="145" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G144" s="8"/>
+      <c r="H144" s="8"/>
+    </row>
+    <row r="145" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="8"/>
       <c r="B145" s="8"/>
       <c r="C145" s="8"/>
       <c r="D145" s="8"/>
       <c r="E145" s="8"/>
       <c r="F145" s="8"/>
-    </row>
-    <row r="146" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G145" s="8"/>
+      <c r="H145" s="8"/>
+    </row>
+    <row r="146" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="8"/>
       <c r="B146" s="8"/>
       <c r="C146" s="8"/>
       <c r="D146" s="8"/>
       <c r="E146" s="8"/>
       <c r="F146" s="8"/>
-    </row>
-    <row r="147" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G146" s="8"/>
+      <c r="H146" s="8"/>
+    </row>
+    <row r="147" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="8"/>
       <c r="B147" s="8"/>
       <c r="C147" s="8"/>
       <c r="D147" s="8"/>
       <c r="E147" s="8"/>
       <c r="F147" s="8"/>
-    </row>
-    <row r="148" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G147" s="8"/>
+      <c r="H147" s="8"/>
+    </row>
+    <row r="148" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="8"/>
       <c r="B148" s="8"/>
       <c r="C148" s="8"/>
       <c r="D148" s="8"/>
       <c r="E148" s="8"/>
       <c r="F148" s="8"/>
-    </row>
-    <row r="149" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G148" s="8"/>
+      <c r="H148" s="8"/>
+    </row>
+    <row r="149" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="8"/>
       <c r="B149" s="8"/>
       <c r="C149" s="8"/>
       <c r="D149" s="8"/>
       <c r="E149" s="8"/>
       <c r="F149" s="8"/>
-    </row>
-    <row r="150" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G149" s="8"/>
+      <c r="H149" s="8"/>
+    </row>
+    <row r="150" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="8"/>
       <c r="B150" s="8"/>
       <c r="C150" s="8"/>
       <c r="D150" s="8"/>
       <c r="E150" s="8"/>
       <c r="F150" s="8"/>
-    </row>
-    <row r="151" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G150" s="8"/>
+      <c r="H150" s="8"/>
+    </row>
+    <row r="151" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="8"/>
       <c r="B151" s="8"/>
       <c r="C151" s="8"/>
       <c r="D151" s="8"/>
       <c r="E151" s="8"/>
       <c r="F151" s="8"/>
-    </row>
-    <row r="152" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G151" s="8"/>
+      <c r="H151" s="8"/>
+    </row>
+    <row r="152" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="8"/>
       <c r="B152" s="8"/>
       <c r="C152" s="8"/>
       <c r="D152" s="8"/>
       <c r="E152" s="8"/>
       <c r="F152" s="8"/>
-    </row>
-    <row r="153" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G152" s="8"/>
+      <c r="H152" s="8"/>
+    </row>
+    <row r="153" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="8"/>
       <c r="B153" s="8"/>
       <c r="C153" s="8"/>
       <c r="D153" s="8"/>
       <c r="E153" s="8"/>
       <c r="F153" s="8"/>
-    </row>
-    <row r="154" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G153" s="8"/>
+      <c r="H153" s="8"/>
+    </row>
+    <row r="154" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="8"/>
       <c r="B154" s="8"/>
       <c r="C154" s="8"/>
       <c r="D154" s="8"/>
       <c r="E154" s="8"/>
       <c r="F154" s="8"/>
-    </row>
-    <row r="155" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G154" s="8"/>
+      <c r="H154" s="8"/>
+    </row>
+    <row r="155" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="8"/>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
       <c r="D155" s="8"/>
       <c r="E155" s="8"/>
       <c r="F155" s="8"/>
-    </row>
-    <row r="156" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G155" s="8"/>
+      <c r="H155" s="8"/>
+    </row>
+    <row r="156" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="8"/>
       <c r="B156" s="8"/>
       <c r="C156" s="8"/>
       <c r="D156" s="8"/>
       <c r="E156" s="8"/>
       <c r="F156" s="8"/>
-    </row>
-    <row r="157" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G156" s="8"/>
+      <c r="H156" s="8"/>
+    </row>
+    <row r="157" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="8"/>
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
       <c r="D157" s="8"/>
       <c r="E157" s="8"/>
       <c r="F157" s="8"/>
-    </row>
-    <row r="158" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G157" s="8"/>
+      <c r="H157" s="8"/>
+    </row>
+    <row r="158" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="8"/>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
       <c r="D158" s="8"/>
       <c r="E158" s="8"/>
       <c r="F158" s="8"/>
-    </row>
-    <row r="159" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G158" s="8"/>
+      <c r="H158" s="8"/>
+    </row>
+    <row r="159" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="8"/>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
       <c r="D159" s="8"/>
       <c r="E159" s="8"/>
       <c r="F159" s="8"/>
-    </row>
-    <row r="160" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G159" s="8"/>
+      <c r="H159" s="8"/>
+    </row>
+    <row r="160" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="8"/>
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
       <c r="D160" s="8"/>
       <c r="E160" s="8"/>
       <c r="F160" s="8"/>
-    </row>
-    <row r="161" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G160" s="8"/>
+      <c r="H160" s="8"/>
+    </row>
+    <row r="161" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="8"/>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
       <c r="D161" s="8"/>
       <c r="E161" s="8"/>
       <c r="F161" s="8"/>
-    </row>
-    <row r="162" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G161" s="8"/>
+      <c r="H161" s="8"/>
+    </row>
+    <row r="162" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="8"/>
       <c r="B162" s="8"/>
       <c r="C162" s="8"/>
       <c r="D162" s="8"/>
       <c r="E162" s="8"/>
       <c r="F162" s="8"/>
-    </row>
-    <row r="163" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G162" s="8"/>
+      <c r="H162" s="8"/>
+    </row>
+    <row r="163" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="8"/>
       <c r="B163" s="8"/>
       <c r="C163" s="8"/>
       <c r="D163" s="8"/>
       <c r="E163" s="8"/>
       <c r="F163" s="8"/>
-    </row>
-    <row r="164" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G163" s="8"/>
+      <c r="H163" s="8"/>
+    </row>
+    <row r="164" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="8"/>
       <c r="B164" s="8"/>
       <c r="C164" s="8"/>
       <c r="D164" s="8"/>
       <c r="E164" s="8"/>
       <c r="F164" s="8"/>
-    </row>
-    <row r="165" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G164" s="8"/>
+      <c r="H164" s="8"/>
+    </row>
+    <row r="165" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="8"/>
       <c r="B165" s="8"/>
       <c r="C165" s="8"/>
       <c r="D165" s="8"/>
       <c r="E165" s="8"/>
       <c r="F165" s="8"/>
-    </row>
-    <row r="166" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G165" s="8"/>
+      <c r="H165" s="8"/>
+    </row>
+    <row r="166" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="8"/>
       <c r="B166" s="8"/>
       <c r="C166" s="8"/>
       <c r="D166" s="8"/>
       <c r="E166" s="8"/>
       <c r="F166" s="8"/>
-    </row>
-    <row r="167" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G166" s="8"/>
+      <c r="H166" s="8"/>
+    </row>
+    <row r="167" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="8"/>
       <c r="B167" s="8"/>
       <c r="C167" s="8"/>
       <c r="D167" s="8"/>
       <c r="E167" s="8"/>
       <c r="F167" s="8"/>
-    </row>
-    <row r="168" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G167" s="8"/>
+      <c r="H167" s="8"/>
+    </row>
+    <row r="168" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="8"/>
       <c r="B168" s="8"/>
       <c r="C168" s="8"/>
       <c r="D168" s="8"/>
       <c r="E168" s="8"/>
       <c r="F168" s="8"/>
-    </row>
-    <row r="169" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G168" s="8"/>
+      <c r="H168" s="8"/>
+    </row>
+    <row r="169" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="8"/>
       <c r="B169" s="8"/>
       <c r="C169" s="8"/>
       <c r="D169" s="8"/>
       <c r="E169" s="8"/>
       <c r="F169" s="8"/>
-    </row>
-    <row r="170" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G169" s="8"/>
+      <c r="H169" s="8"/>
+    </row>
+    <row r="170" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="8"/>
       <c r="B170" s="8"/>
       <c r="C170" s="8"/>
       <c r="D170" s="8"/>
       <c r="E170" s="8"/>
       <c r="F170" s="8"/>
-    </row>
-    <row r="171" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G170" s="8"/>
+      <c r="H170" s="8"/>
+    </row>
+    <row r="171" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="8"/>
       <c r="B171" s="8"/>
       <c r="C171" s="8"/>
       <c r="D171" s="8"/>
       <c r="E171" s="8"/>
       <c r="F171" s="8"/>
-    </row>
-    <row r="172" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G171" s="8"/>
+      <c r="H171" s="8"/>
+    </row>
+    <row r="172" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="8"/>
       <c r="B172" s="8"/>
       <c r="C172" s="8"/>
       <c r="D172" s="8"/>
       <c r="E172" s="8"/>
       <c r="F172" s="8"/>
-    </row>
-    <row r="173" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G172" s="8"/>
+      <c r="H172" s="8"/>
+    </row>
+    <row r="173" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="8"/>
       <c r="B173" s="8"/>
       <c r="C173" s="8"/>
       <c r="D173" s="8"/>
       <c r="E173" s="8"/>
       <c r="F173" s="8"/>
-    </row>
-    <row r="174" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1">
+      <c r="G173" s="8"/>
+      <c r="H173" s="8"/>
+    </row>
+    <row r="174" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="8"/>
       <c r="B174" s="8"/>
       <c r="C174" s="8"/>
       <c r="D174" s="8"/>
       <c r="E174" s="8"/>
       <c r="F174" s="8"/>
+      <c r="G174" s="8"/>
+      <c r="H174" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="F2:G2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/水库项目出表/Template/图斑量算表.xlsx
+++ b/水库项目出表/Template/图斑量算表.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>图斑量算表</t>
   </si>
@@ -58,6 +58,10 @@
   </si>
   <si>
     <t>单位：#单位#</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>地类名称</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -505,18 +509,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H174"/>
+  <dimension ref="A1:I174"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.453125" style="3" customWidth="1"/>
     <col min="2" max="2" width="8.453125" style="3" customWidth="1"/>
     <col min="3" max="7" width="12.36328125" style="3" customWidth="1"/>
     <col min="8" max="8" width="11.26953125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="9" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.26953125" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -527,8 +531,9 @@
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
-    </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I1" s="10"/>
+    </row>
+    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -538,11 +543,11 @@
         <v>1</v>
       </c>
       <c r="G2" s="11"/>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -553,22 +558,25 @@
         <v>4</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -577,6 +585,7 @@
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
     </row>
     <row r="97" spans="1:8" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="8"/>
@@ -1360,8 +1369,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:H1"/>
     <mergeCell ref="F2:G2"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
